--- a/data/excel/16-pingtung.xlsx
+++ b/data/excel/16-pingtung.xlsx
@@ -872,7 +872,6 @@
           <t>2026-04-20</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1273,8 +1272,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:D65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
@@ -1297,6 +1302,1158 @@
           <t>note</t>
         </is>
       </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>屏東市</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>屏東市區</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>商圈</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>屏東市</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>勝利路商圈</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>商圈</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>屏東市</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>屏東火車站</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>商圈</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>屏東市</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>中山路</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>商圈</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>潮州鎮</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>潮州市區</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>商圈</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>潮州鎮</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>潮州老街</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>商圈</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>潮州鎮</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>中山路</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>商圈</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>潮州鎮</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>信義路</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>商圈</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>東港鎮</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>東港漁港</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>商圈</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>東港鎮</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>東港老街</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>商圈</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>東港鎮</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>中山路</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>商圈</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>東港鎮</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>黑鮪魚文化節</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>商圈</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>恆春鎮</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>恆春老城</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>商圈</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>恆春鎮</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>南灣</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>商圈</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>恆春鎮</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>墾丁大街</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>商圈</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>恆春鎮</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>中正路</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>商圈</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>萬丹鄉</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>萬丹市區</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>商圈</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>萬丹鄉</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>中山路</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>商圈</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>萬丹鄉</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>土庫村</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>商圈</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>萬丹鄉</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>社口村</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>商圈</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>內埔鄉</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>內埔市區</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>商圈</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>內埔鄉</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>中山路</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>商圈</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>內埔鄉</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>六堆客家</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>商圈</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>內埔鄉</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>竹田交界</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>商圈</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>萬巒鄉</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>萬巒豬腳街</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>商圈</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>萬巒鄉</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>萬巒市區</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>商圈</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>萬巒鄉</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>中山路</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>商圈</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>萬巒鄉</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>赤山村</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>商圈</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>琉球鄉</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>小琉球漁港</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>商圈</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>琉球鄉</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>美人洞</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>商圈</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>琉球鄉</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>厚石群礁</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>商圈</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>琉球鄉</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>白燈塔</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>商圈</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>高樹鄉</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>高樹市區</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>商圈</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>高樹鄉</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>中山路</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>商圈</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>高樹鄉</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>廣福村</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>商圈</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>高樹鄉</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>泰山村</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>商圈</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>里港鄉</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>里港市區</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>商圈</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>里港鄉</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>里港老街</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>商圈</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>里港鄉</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>中山路</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>商圈</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>里港鄉</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>鄉公所</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>商圈</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>長治鄉</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>長治市區</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>商圈</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>長治鄉</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>中山路</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>商圈</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>長治鄉</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>繁華村</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>商圈</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>長治鄉</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>香社村</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>商圈</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>竹田鄉</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>竹田市區</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>商圈</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>竹田鄉</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>中山路</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>商圈</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>竹田鄉</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>六堆客家</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>商圈</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>竹田鄉</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>地磨兒</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>商圈</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>林邊鄉</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>林邊市區</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>商圈</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>林邊鄉</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>林邊火車站</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>商圈</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>林邊鄉</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>中山路</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>商圈</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>林邊鄉</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>崎峰村</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>商圈</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>佳冬鄉</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>佳冬市區</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>商圈</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>佳冬鄉</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>六根村</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>商圈</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>佳冬鄉</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>中山路</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>商圈</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>佳冬鄉</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>客家聚落</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>商圈</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>枋寮鄉</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>枋寮市區</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>商圈</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>枋寮鄉</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>枋寮漁港</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>商圈</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>枋寮鄉</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>中山路</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>商圈</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>枋寮鄉</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>火車站</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>商圈</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>新園鄉</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>新園市區</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>商圈</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>新園鄉</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>中山路</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>商圈</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>新園鄉</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>五房村</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>商圈</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>新園鄉</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>港埔村</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>商圈</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/excel/16-pingtung.xlsx
+++ b/data/excel/16-pingtung.xlsx
@@ -1272,7 +1272,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D65"/>
+  <dimension ref="A1:D133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1319,7 +1319,6 @@
           <t>商圈</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1337,7 +1336,6 @@
           <t>商圈</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1355,7 +1353,6 @@
           <t>商圈</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1373,7 +1370,6 @@
           <t>商圈</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1391,7 +1387,6 @@
           <t>商圈</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1409,7 +1404,6 @@
           <t>商圈</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1427,7 +1421,6 @@
           <t>商圈</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1445,7 +1438,6 @@
           <t>商圈</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1463,7 +1455,6 @@
           <t>商圈</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1481,7 +1472,6 @@
           <t>商圈</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1499,7 +1489,6 @@
           <t>商圈</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1517,7 +1506,6 @@
           <t>商圈</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1535,7 +1523,6 @@
           <t>商圈</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1553,7 +1540,6 @@
           <t>商圈</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1571,7 +1557,6 @@
           <t>商圈</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1589,7 +1574,6 @@
           <t>商圈</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1607,7 +1591,6 @@
           <t>商圈</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1625,7 +1608,6 @@
           <t>商圈</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1643,7 +1625,6 @@
           <t>商圈</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1661,17 +1642,16 @@
           <t>商圈</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>內埔鄉</t>
+          <t>長治鄉</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>內埔市區</t>
+          <t>長治市區</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1679,12 +1659,11 @@
           <t>商圈</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>內埔鄉</t>
+          <t>長治鄉</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1697,17 +1676,16 @@
           <t>商圈</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>內埔鄉</t>
+          <t>長治鄉</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>六堆客家</t>
+          <t>繁華村</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1715,17 +1693,16 @@
           <t>商圈</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>內埔鄉</t>
+          <t>長治鄉</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>竹田交界</t>
+          <t>香社村</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1733,17 +1710,16 @@
           <t>商圈</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>萬巒鄉</t>
+          <t>麟洛鄉</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>萬巒豬腳街</t>
+          <t>麟洛市區</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1751,17 +1727,16 @@
           <t>商圈</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>萬巒鄉</t>
+          <t>麟洛鄉</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>萬巒市區</t>
+          <t>中山路</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1769,17 +1744,16 @@
           <t>商圈</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>萬巒鄉</t>
+          <t>麟洛鄉</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>中山路</t>
+          <t>田道村</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1787,17 +1761,16 @@
           <t>商圈</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>萬巒鄉</t>
+          <t>麟洛鄉</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>赤山村</t>
+          <t>麟洛公園</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1805,17 +1778,16 @@
           <t>商圈</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>琉球鄉</t>
+          <t>九如鄉</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>小琉球漁港</t>
+          <t>九如市區</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1823,17 +1795,16 @@
           <t>商圈</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>琉球鄉</t>
+          <t>九如鄉</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>美人洞</t>
+          <t>中山路</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1841,17 +1812,16 @@
           <t>商圈</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>琉球鄉</t>
+          <t>九如鄉</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>厚石群礁</t>
+          <t>九明村</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1859,17 +1829,16 @@
           <t>商圈</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>琉球鄉</t>
+          <t>九如鄉</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>白燈塔</t>
+          <t>玉泉村</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1877,17 +1846,16 @@
           <t>商圈</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>高樹鄉</t>
+          <t>里港鄉</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>高樹市區</t>
+          <t>里港市區</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1895,17 +1863,16 @@
           <t>商圈</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>高樹鄉</t>
+          <t>里港鄉</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>中山路</t>
+          <t>里港老街</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1913,17 +1880,16 @@
           <t>商圈</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>高樹鄉</t>
+          <t>里港鄉</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>廣福村</t>
+          <t>中山路</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1931,17 +1897,16 @@
           <t>商圈</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>高樹鄉</t>
+          <t>里港鄉</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>泰山村</t>
+          <t>鄉公所</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1949,17 +1914,16 @@
           <t>商圈</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>里港鄉</t>
+          <t>鹽埔鄉</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>里港市區</t>
+          <t>鹽埔市區</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1967,17 +1931,16 @@
           <t>商圈</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>里港鄉</t>
+          <t>鹽埔鄉</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>里港老街</t>
+          <t>中山路</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1985,17 +1948,16 @@
           <t>商圈</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>里港鄉</t>
+          <t>鹽埔鄉</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>中山路</t>
+          <t>彭厝村</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2003,17 +1965,16 @@
           <t>商圈</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>里港鄉</t>
+          <t>鹽埔鄉</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>鄉公所</t>
+          <t>新圍村</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2021,17 +1982,16 @@
           <t>商圈</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>長治鄉</t>
+          <t>高樹鄉</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>長治市區</t>
+          <t>高樹市區</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2039,12 +1999,11 @@
           <t>商圈</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>長治鄉</t>
+          <t>高樹鄉</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2057,17 +2016,16 @@
           <t>商圈</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>長治鄉</t>
+          <t>高樹鄉</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>繁華村</t>
+          <t>廣福村</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2075,17 +2033,16 @@
           <t>商圈</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>長治鄉</t>
+          <t>高樹鄉</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>香社村</t>
+          <t>泰山村</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2093,17 +2050,16 @@
           <t>商圈</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>竹田鄉</t>
+          <t>萬巒鄉</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>竹田市區</t>
+          <t>萬巒豬腳街</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2111,17 +2067,16 @@
           <t>商圈</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>竹田鄉</t>
+          <t>萬巒鄉</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>中山路</t>
+          <t>萬巒市區</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2129,17 +2084,16 @@
           <t>商圈</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>竹田鄉</t>
+          <t>萬巒鄉</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>六堆客家</t>
+          <t>中山路</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2147,17 +2101,16 @@
           <t>商圈</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>竹田鄉</t>
+          <t>萬巒鄉</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>地磨兒</t>
+          <t>赤山村</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2165,17 +2118,16 @@
           <t>商圈</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>林邊鄉</t>
+          <t>內埔鄉</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>林邊市區</t>
+          <t>內埔市區</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2183,17 +2135,16 @@
           <t>商圈</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>林邊鄉</t>
+          <t>內埔鄉</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>林邊火車站</t>
+          <t>中山路</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2201,17 +2152,16 @@
           <t>商圈</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>林邊鄉</t>
+          <t>內埔鄉</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>中山路</t>
+          <t>六堆客家</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2219,17 +2169,16 @@
           <t>商圈</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>林邊鄉</t>
+          <t>內埔鄉</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>崎峰村</t>
+          <t>竹田交界</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2237,17 +2186,16 @@
           <t>商圈</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>佳冬鄉</t>
+          <t>竹田鄉</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>佳冬市區</t>
+          <t>竹田市區</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2255,17 +2203,16 @@
           <t>商圈</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>佳冬鄉</t>
+          <t>竹田鄉</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>六根村</t>
+          <t>中山路</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2273,17 +2220,16 @@
           <t>商圈</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>佳冬鄉</t>
+          <t>竹田鄉</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>中山路</t>
+          <t>六堆客家</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2291,17 +2237,16 @@
           <t>商圈</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>佳冬鄉</t>
+          <t>竹田鄉</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>客家聚落</t>
+          <t>地磨兒</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2309,17 +2254,16 @@
           <t>商圈</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>枋寮鄉</t>
+          <t>新埤鄉</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>枋寮市區</t>
+          <t>新埤市區</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2327,17 +2271,16 @@
           <t>商圈</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>枋寮鄉</t>
+          <t>新埤鄉</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>枋寮漁港</t>
+          <t>中山路</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2345,17 +2288,16 @@
           <t>商圈</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>枋寮鄉</t>
+          <t>新埤鄉</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>中山路</t>
+          <t>餉潭村</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2363,17 +2305,16 @@
           <t>商圈</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>枋寮鄉</t>
+          <t>新埤鄉</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>火車站</t>
+          <t>建功村</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2381,17 +2322,16 @@
           <t>商圈</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>新園鄉</t>
+          <t>枋寮鄉</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>新園市區</t>
+          <t>枋寮市區</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2399,17 +2339,16 @@
           <t>商圈</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>新園鄉</t>
+          <t>枋寮鄉</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>中山路</t>
+          <t>枋寮漁港</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2417,17 +2356,16 @@
           <t>商圈</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>新園鄉</t>
+          <t>枋寮鄉</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>五房村</t>
+          <t>中山路</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2435,25 +2373,1179 @@
           <t>商圈</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
+          <t>枋寮鄉</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>火車站</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>商圈</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
           <t>新園鄉</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr">
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>新園市區</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>商圈</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>新園鄉</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>中山路</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>商圈</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>新園鄉</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>五房村</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>商圈</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>新園鄉</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
         <is>
           <t>港埔村</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>商圈</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr"/>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>商圈</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>崁頂鄉</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>崁頂市區</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>商圈</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>崁頂鄉</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>中山路</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>商圈</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>崁頂鄉</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>力社村</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>商圈</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>崁頂鄉</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>越溪村</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>商圈</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>林邊鄉</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>林邊市區</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>商圈</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>林邊鄉</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>林邊火車站</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>商圈</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>林邊鄉</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>中山路</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>商圈</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>林邊鄉</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>崎峰村</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>商圈</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>南州鄉</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>南州市區</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>商圈</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>南州鄉</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>中山路</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>商圈</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>南州鄉</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>萬華村</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>商圈</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>南州鄉</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>溪北村</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>商圈</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>佳冬鄉</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>佳冬市區</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>商圈</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>佳冬鄉</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>六根村</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>商圈</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>佳冬鄉</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>中山路</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>商圈</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>佳冬鄉</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>客家聚落</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>商圈</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>琉球鄉</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>小琉球漁港</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>商圈</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>琉球鄉</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>美人洞</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>商圈</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>琉球鄉</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>厚石群礁</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>商圈</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>琉球鄉</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>白燈塔</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>商圈</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>車城鄉</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>車城市區</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>商圈</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>車城鄉</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>四重溪溫泉</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>商圈</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>車城鄉</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>中山路</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>商圈</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>車城鄉</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>福安宮</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>商圈</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>滿州鄉</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>滿州市區</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>商圈</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>滿州鄉</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>港口茶</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>商圈</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>滿州鄉</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>中山路</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>商圈</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>滿州鄉</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>九棚</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>商圈</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>枋山鄉</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>枋山市區</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>商圈</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>枋山鄉</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>楓港</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>商圈</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>枋山鄉</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>中山路</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>商圈</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>枋山鄉</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>善餘村</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>商圈</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>三地門鄉</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>三地門市區</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>商圈</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>三地門鄉</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>青葉部落</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>商圈</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>三地門鄉</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>中山路</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>商圈</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>三地門鄉</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>德文村</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>商圈</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>霧台鄉</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>霧台市區</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>商圈</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>霧台鄉</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>阿禮部落</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>商圈</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>霧台鄉</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>神山瀑布</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>商圈</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>霧台鄉</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>好茶</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>商圈</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>瑪家鄉</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>瑪家市區</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>商圈</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>瑪家鄉</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>原住民文化園區</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>商圈</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>瑪家鄉</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>中山路</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>商圈</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>瑪家鄉</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>北葉</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>商圈</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>泰武鄉</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>泰武市區</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>商圈</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>泰武鄉</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>中山路</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>商圈</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>泰武鄉</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>佳平部落</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>商圈</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>泰武鄉</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>武潭</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>商圈</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>來義鄉</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>來義市區</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>商圈</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>來義鄉</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>中山路</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>商圈</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>來義鄉</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>古樓村</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>商圈</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>來義鄉</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>文樂</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>商圈</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>春日鄉</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>春日市區</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>商圈</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>春日鄉</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>七佳部落</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>商圈</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>春日鄉</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>中山路</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>商圈</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>春日鄉</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>古仁</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>商圈</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>獅子鄉</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>獅子市區</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>商圈</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>獅子鄉</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>楓林村</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>商圈</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>獅子鄉</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>中山路</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>商圈</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>獅子鄉</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>內文</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>商圈</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>牡丹鄉</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>牡丹市區</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>商圈</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>牡丹鄉</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>旭海</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>商圈</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>牡丹鄉</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>中山路</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>商圈</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>牡丹鄉</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>石門古戰場</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>商圈</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
